--- a/release/Web_All_StringTable_20260911.xlsx
+++ b/release/Web_All_StringTable_20260911.xlsx
@@ -10,7 +10,7 @@
     <sheet name="X6ES" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">X6ES!$A$1:$R$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">X6ES!$A$1:$R$681</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -12032,7 +12032,7 @@
     <t>wifi.dfsWeatherRaderOn</t>
   </si>
   <si>
-    <t>DFS/Weather Rader On</t>
+    <t>DFS/Weather Radar On</t>
   </si>
   <si>
     <t>DFS/天氣雷達開啟</t>
@@ -30286,6 +30286,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>此</t>
     </r>
     <r>
@@ -31057,7 +31062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -31080,9 +31085,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -37125,10 +37127,10 @@
       <c r="O102" s="7" t="s">
         <v>1516</v>
       </c>
-      <c r="P102" s="8" t="s">
+      <c r="P102" s="6" t="s">
         <v>1517</v>
       </c>
-      <c r="Q102" s="9" t="s">
+      <c r="Q102" s="8" t="s">
         <v>1518</v>
       </c>
       <c r="R102" s="5" t="s">
@@ -46436,7 +46438,7 @@
       <c r="B269" s="6" t="s">
         <v>4022</v>
       </c>
-      <c r="C269" s="9" t="s">
+      <c r="C269" s="8" t="s">
         <v>4023</v>
       </c>
       <c r="D269" s="6" t="s">
@@ -46457,7 +46459,7 @@
       <c r="I269" s="6" t="s">
         <v>4029</v>
       </c>
-      <c r="J269" s="9" t="s">
+      <c r="J269" s="8" t="s">
         <v>4030</v>
       </c>
       <c r="K269" s="6" t="s">
@@ -46478,7 +46480,7 @@
       <c r="P269" s="6" t="s">
         <v>4036</v>
       </c>
-      <c r="Q269" s="9" t="s">
+      <c r="Q269" s="8" t="s">
         <v>4037</v>
       </c>
       <c r="R269" s="6" t="s">
@@ -49964,7 +49966,7 @@
       <c r="B332" s="6" t="s">
         <v>4995</v>
       </c>
-      <c r="C332" s="9" t="s">
+      <c r="C332" s="8" t="s">
         <v>4996</v>
       </c>
       <c r="D332" s="6" t="s">
@@ -49985,7 +49987,7 @@
       <c r="I332" s="6" t="s">
         <v>4998</v>
       </c>
-      <c r="J332" s="9" t="s">
+      <c r="J332" s="8" t="s">
         <v>5002</v>
       </c>
       <c r="K332" s="6" t="s">
@@ -50006,7 +50008,7 @@
       <c r="P332" s="6" t="s">
         <v>5008</v>
       </c>
-      <c r="Q332" s="9" t="s">
+      <c r="Q332" s="8" t="s">
         <v>5009</v>
       </c>
       <c r="R332" s="6" t="s">
@@ -69447,60 +69449,60 @@
       <c r="A681" s="1" t="s">
         <v>10047</v>
       </c>
-      <c r="B681" s="10" t="s">
+      <c r="B681" s="9" t="s">
         <v>10048</v>
       </c>
-      <c r="C681" s="11" t="s">
+      <c r="C681" s="10" t="s">
         <v>10049</v>
       </c>
-      <c r="D681" s="10" t="s">
+      <c r="D681" s="9" t="s">
         <v>10050</v>
       </c>
-      <c r="E681" s="10" t="s">
+      <c r="E681" s="9" t="s">
         <v>10051</v>
       </c>
-      <c r="F681" s="10" t="s">
+      <c r="F681" s="9" t="s">
         <v>10052</v>
       </c>
-      <c r="G681" s="10" t="s">
+      <c r="G681" s="9" t="s">
         <v>10053</v>
       </c>
-      <c r="H681" s="10" t="s">
+      <c r="H681" s="9" t="s">
         <v>10054</v>
       </c>
-      <c r="I681" s="10" t="s">
+      <c r="I681" s="9" t="s">
         <v>10051</v>
       </c>
-      <c r="J681" s="10" t="s">
+      <c r="J681" s="9" t="s">
         <v>10055</v>
       </c>
-      <c r="K681" s="10" t="s">
+      <c r="K681" s="9" t="s">
         <v>10056</v>
       </c>
-      <c r="L681" s="10" t="s">
+      <c r="L681" s="9" t="s">
         <v>10055</v>
       </c>
-      <c r="M681" s="10" t="s">
+      <c r="M681" s="9" t="s">
         <v>10057</v>
       </c>
-      <c r="N681" s="10" t="s">
+      <c r="N681" s="9" t="s">
         <v>10058</v>
       </c>
-      <c r="O681" s="10" t="s">
+      <c r="O681" s="9" t="s">
         <v>10059</v>
       </c>
-      <c r="P681" s="10" t="s">
+      <c r="P681" s="9" t="s">
         <v>10060</v>
       </c>
-      <c r="Q681" s="10" t="s">
+      <c r="Q681" s="9" t="s">
         <v>10061</v>
       </c>
-      <c r="R681" s="10" t="s">
+      <c r="R681" s="9" t="s">
         <v>10062</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R680">
+  <autoFilter ref="A1:R681">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
